--- a/data/extracted_receipts.xlsx
+++ b/data/extracted_receipts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1036,16 +1036,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cold Ocha</t>
+          <t>SQUADES 19 LTR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1053,24 +1053,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F22" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G22" t="n">
-        <v>713048</v>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bottled Water</t>
+          <t>PASEO BATHROOMN 12 ROL</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1082,24 +1080,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8000</v>
+        <v>81000</v>
       </c>
       <c r="F23" t="n">
-        <v>16000</v>
-      </c>
-      <c r="G23" t="n">
-        <v>713048</v>
-      </c>
+        <v>81000</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Chicken Katsu Ju</t>
+          <t>PASEO BABY SOFT PACK 130'S</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1111,24 +1107,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>68000</v>
+        <v>17500</v>
       </c>
       <c r="F24" t="n">
-        <v>68000</v>
-      </c>
-      <c r="G24" t="n">
-        <v>713048</v>
-      </c>
+        <v>17500</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chuka Wakame</t>
+          <t>CAREFREE S.DRY BRE UNS 40'S</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1140,24 +1134,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>50000</v>
+        <v>26800</v>
       </c>
       <c r="F25" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G25" t="n">
-        <v>713048</v>
-      </c>
+        <v>26800</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Salmon 3 Slice SSM</t>
+          <t>LAURIER RN GATHERS 35CM 16P</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1169,24 +1161,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>55000</v>
+        <v>28700</v>
       </c>
       <c r="F26" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G26" t="n">
-        <v>713048</v>
-      </c>
+        <v>28700</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Yasai Tempura</t>
+          <t>PASEO WET 25'S ANTI BACTERI</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1198,28 +1188,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>43000</v>
+        <v>8600</v>
       </c>
       <c r="F27" t="n">
-        <v>43000</v>
-      </c>
-      <c r="G27" t="n">
-        <v>713048</v>
-      </c>
+        <v>8600</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Salmon Don</t>
+          <t>PASEO WIPS ANTI BACTERIAL 5</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1227,24 +1215,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>99000</v>
+        <v>8600</v>
       </c>
       <c r="F28" t="n">
-        <v>198000</v>
-      </c>
-      <c r="G28" t="n">
-        <v>713048</v>
-      </c>
+        <v>8600</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chocoyama Mint</t>
+          <t>SUNLIGHT 610 ML REFF LIME</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1256,24 +1242,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>41000</v>
+        <v>9700</v>
       </c>
       <c r="F29" t="n">
-        <v>41000</v>
-      </c>
-      <c r="G29" t="n">
-        <v>713048</v>
-      </c>
+        <v>9700</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>CAREX HW 200 ML REF ALOE VE</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1285,41 +1269,651 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>65000</v>
+        <v>22000</v>
       </c>
       <c r="F30" t="n">
-        <v>65000</v>
-      </c>
-      <c r="G30" t="n">
-        <v>713048</v>
-      </c>
+        <v>22000</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MOLTO PURE 550ML</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>15600</v>
+      </c>
+      <c r="F31" t="n">
+        <v>31200</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TAF 500 ML FRESH BLUE</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F32" t="n">
+        <v>23000</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>REBEK KLOSET 450 ML BTL PIN</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>21200</v>
+      </c>
+      <c r="F33" t="n">
+        <v>21200</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LISTERINE 500ML COOL MINT T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>65900</v>
+      </c>
+      <c r="F34" t="n">
+        <v>131800</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JSF NORI TABUR ORIGINAL 60</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>18300</v>
+      </c>
+      <c r="F35" t="n">
+        <v>18300</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>VANISH 425 ML REF PINK</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>24500</v>
+      </c>
+      <c r="F36" t="n">
+        <v>24500</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SOKLIN LIQ 700 ML VIOLET</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>17000</v>
+      </c>
+      <c r="F37" t="n">
+        <v>17000</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DAECHUN WANGGA 3X4.5GR ORIG</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>14600</v>
+      </c>
+      <c r="F38" t="n">
+        <v>14600</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TONG TJI TEH MELATI NV 25X2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>10600</v>
+      </c>
+      <c r="F39" t="n">
+        <v>10600</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PEPSODENT TP 100GR SENS EP</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>33500</v>
+      </c>
+      <c r="F40" t="n">
+        <v>33500</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>KLINPAK KANTONG SAMPAH KECI</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>29800</v>
+      </c>
+      <c r="F41" t="n">
+        <v>29800</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ULTRA MILK 1.000 ML PLAIN(1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F42" t="n">
+        <v>23000</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>QUAKER 800 GR INSTANT</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>49700</v>
+      </c>
+      <c r="F43" t="n">
+        <v>49700</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>2024-06-16</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cold Ocha</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F44" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G44" t="n">
+        <v>713048</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Bottled Water</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F45" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>713048</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Chicken Katsu Ju</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>68000</v>
+      </c>
+      <c r="F46" t="n">
+        <v>68000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>713048</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Chuka Wakame</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F47" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G47" t="n">
+        <v>713048</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Salmon 3 Slice SSM</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>55000</v>
+      </c>
+      <c r="F48" t="n">
+        <v>55000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>713048</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Yasai Tempura</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>43000</v>
+      </c>
+      <c r="F49" t="n">
+        <v>43000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>713048</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Salmon Don</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>99000</v>
+      </c>
+      <c r="F50" t="n">
+        <v>198000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>713048</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Chocoyama Mint</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>41000</v>
+      </c>
+      <c r="F51" t="n">
+        <v>41000</v>
+      </c>
+      <c r="G51" t="n">
+        <v>713048</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F52" t="n">
+        <v>65000</v>
+      </c>
+      <c r="G52" t="n">
+        <v>713048</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>(TA) Matcha Yuzu</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
         <v>47000</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F53" t="n">
         <v>47000</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G53" t="n">
         <v>713048</v>
       </c>
     </row>
